--- a/backend/static/excel_data/962677eff8fe7619c70e350c7a754506/single_1.xlsx
+++ b/backend/static/excel_data/962677eff8fe7619c70e350c7a754506/single_1.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>普通表格_962677eff8fe7619c70e350c7a754506_001_table_1</t>
+          <t>作文评分记录</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,33 +544,52 @@
           <t>教师评语</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>表格名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>吕琳</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -582,33 +601,52 @@
           <t>续写与原文衔接自然，词汇灵活</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>李洋</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -620,33 +658,52 @@
           <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>张琴</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -658,33 +715,52 @@
           <t>偏离原文少许，但表达尚清楚</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>张红梅</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>16</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -696,33 +772,52 @@
           <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>王东</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>18</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -734,33 +829,52 @@
           <t>句式较单一，字数刚好，书写可提高。</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>邹春梅</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -772,33 +886,52 @@
           <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>王丽</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>16</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -810,33 +943,52 @@
           <t>内容贴合原文，句式丰富，卷面清爽。</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>徐玲</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -848,33 +1000,52 @@
           <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>李慧</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>20</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -886,33 +1057,52 @@
           <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>魏秀梅</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>16</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -924,33 +1114,52 @@
           <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>阎阳</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -962,33 +1171,52 @@
           <t>内容基本相关，结构需更紧凑。</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>安敏</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>18</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1000,33 +1228,52 @@
           <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>杨红</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>14</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1038,33 +1285,52 @@
           <t>续写与原文衔接自然，词汇灵活。</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>亓敏</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>18</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1076,33 +1342,52 @@
           <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>郑秀华</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>16</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1114,33 +1399,52 @@
           <t>情节合理，语言流畅，书写工整。</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>孙东</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>17</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1152,33 +1456,52 @@
           <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>姚春梅</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>18</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1190,33 +1513,52 @@
           <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>杨秀兰</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>17</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1228,33 +1570,52 @@
           <t>偏离原文少许，但表达尚清楚</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>马莹</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>18</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1266,33 +1627,52 @@
           <t>主题明确，逻辑清晰，书写再工整些更佳。</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>夏亮</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>17</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1304,33 +1684,52 @@
           <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>杨欢</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>18</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1342,33 +1741,52 @@
           <t>故事完整，结构紧凑，表达有亮点。</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>李静</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>18</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1380,33 +1798,52 @@
           <t>句式较单一，字数刚好，书写可提高。</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>陈建平</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>17</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1418,33 +1855,52 @@
           <t>情节略显突兀，语言可读性较好。</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>李淑珍</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>14</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1456,33 +1912,52 @@
           <t>细节生动，结尾有力，略有小错。</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>陈凤英</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>17</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1494,33 +1969,52 @@
           <t>内容基本相关，结构需更紧凑。</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>陈凤兰</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>17</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1530,6 +2024,11 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>句式较单一，字数刚好，书写可提高。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>作文评分记录</t>
         </is>
       </c>
     </row>
